--- a/surveyor_forms/001_skincare_questionnaire--surveyor_forms.xlsx
+++ b/surveyor_forms/001_skincare_questionnaire--surveyor_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -525,36 +525,36 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>User Input</t>
+          <t>What is your name?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>age</t>
+          <t>user_input2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Age</t>
+          <t>How often do you use skincare products?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -566,41 +566,41 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>email_input</t>
+          <t>user_input3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>What is your age?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>select_input1</t>
+          <t>email_input1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Select Input 1</t>
+          <t>How would you like to be contacted for follow-up questions?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -612,18 +612,18 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>select_input2</t>
+          <t>select_input1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Select Input 2</t>
+          <t>Which skincare routine is most important to you?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -635,18 +635,18 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>date_input</t>
+          <t>date_input1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>On what date did you last use a skincare product?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -658,18 +658,18 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>time_input</t>
+          <t>time_input1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Time</t>
+          <t>At what time of day do you prefer to use skincare products?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -681,18 +681,18 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>note_input</t>
+          <t>note_input1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Note</t>
+          <t>What is your current skincare note?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -709,7 +709,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Phone 1</t>
+          <t>What is your primary phone number?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -732,7 +732,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Phone 2</t>
+          <t>What is your secondary phone number?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -745,320 +745,44 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>email_input</t>
+          <t>user_input4</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>How do you rate your current skin condition?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>user_input2</t>
+          <t>user_input5</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>User Input 2</t>
+          <t>Additional comments or notes</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>select_input3</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Select Input 3</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>select_input4</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Select Input 4</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>user_input3</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>User Input 3</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>date_input</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>time_input</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Time</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>note_input</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Note</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>phone_input1</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Phone 1</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>phone_input2</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Phone 2</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>email_input</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>user_input4</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>User Input 4</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>select_input5</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Select Input 5</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>select_input6</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Select Input 6</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1075,12 +799,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1103,306 +827,187 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>select_input1_choices</t>
+          <t>user_input2_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'option_1',_'label':_'option_1'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Option 1', 'label': 'Option 1'}</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>select_input1_choices</t>
+          <t>user_input2_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'option_2',_'label':_'option_2'}</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Option 2', 'label': 'Option 2'}</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>select_input1_choices</t>
+          <t>user_input2_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'option_3',_'label':_'option_3'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Option 3', 'label': 'Option 3'}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>select_input2_choices</t>
+          <t>select_input1_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'option_4',_'label':_'option_4'}</t>
+          <t>cleansing</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Option 4', 'label': 'Option 4'}</t>
+          <t>Cleansing</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_input2_choices</t>
+          <t>select_input1_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'option_5',_'label':_'option_5'}</t>
+          <t>moisturizing</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'Option 5', 'label': 'Option 5'}</t>
+          <t>Moisturizing</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_input2_choices</t>
+          <t>select_input1_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_6,_'name':_'option_6',_'label':_'option_6'}</t>
+          <t>exfoliating</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 6, 'name': 'Option 6', 'label': 'Option 6'}</t>
+          <t>Exfoliating</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_input3_choices</t>
+          <t>select_input1_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_7,_'name':_'option_7',_'label':_'option_7'}</t>
+          <t>masking</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 7, 'name': 'Option 7', 'label': 'Option 7'}</t>
+          <t>Masking</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_input3_choices</t>
+          <t>user_input4_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_8,_'name':_'option_8',_'label':_'option_8'}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 8, 'name': 'Option 8', 'label': 'Option 8'}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_input3_choices</t>
+          <t>user_input4_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_9,_'name':_'option_9',_'label':_'option_9'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 9, 'name': 'Option 9', 'label': 'Option 9'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_input4_choices</t>
+          <t>user_input4_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_10,_'name':_'option_10',_'label':_'option_10'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 10, 'name': 'Option 10', 'label': 'Option 10'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_input4_choices</t>
+          <t>user_input4_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_11,_'name':_'option_11',_'label':_'option_11'}</t>
+          <t>bad</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 11, 'name': 'Option 11', 'label': 'Option 11'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>select_input4_choices</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>{'id':_12,_'name':_'option_12',_'label':_'option_12'}</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>{'id': 12, 'name': 'Option 12', 'label': 'Option 12'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>select_input5_choices</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>{'id':_13,_'name':_'option_13',_'label':_'option_13'}</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>{'id': 13, 'name': 'Option 13', 'label': 'Option 13'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>select_input5_choices</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>{'id':_14,_'name':_'option_14',_'label':_'option_14'}</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>{'id': 14, 'name': 'Option 14', 'label': 'Option 14'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>select_input5_choices</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>{'id':_15,_'name':_'option_15',_'label':_'option_15'}</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>{'id': 15, 'name': 'Option 15', 'label': 'Option 15'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>select_input6_choices</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>{'id':_16,_'name':_'option_16',_'label':_'option_16'}</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>{'id': 16, 'name': 'Option 16', 'label': 'Option 16'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>select_input6_choices</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>{'id':_17,_'name':_'option_17',_'label':_'option_17'}</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>{'id': 17, 'name': 'Option 17', 'label': 'Option 17'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>select_input6_choices</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>{'id':_18,_'name':_'option_18',_'label':_'option_18'}</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>{'id': 18, 'name': 'Option 18', 'label': 'Option 18'}</t>
+          <t>Bad</t>
         </is>
       </c>
     </row>
